--- a/reports/Master_Report.xlsx
+++ b/reports/Master_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="328">
   <si>
     <t>QA Testing Metrics</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Run Timestamp</t>
   </si>
   <si>
-    <t>6/16/2026, 4:22:33 AM</t>
+    <t>6/16/2026, 4:28:43 AM</t>
   </si>
   <si>
     <t>Selenium E2E Passed</t>
@@ -100,7 +100,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.67s</t>
+    <t>0.65s</t>
   </si>
   <si>
     <t>TC-SEL-02</t>
@@ -112,7 +112,7 @@
     <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
   </si>
   <si>
-    <t>0.59s</t>
+    <t>0.62s</t>
   </si>
   <si>
     <t>TC-SEL-03</t>
@@ -124,21 +124,21 @@
     <t>Error message: "Password must be at least 8 characters." displays</t>
   </si>
   <si>
+    <t>0.52s</t>
+  </si>
+  <si>
+    <t>TC-SEL-04</t>
+  </si>
+  <si>
+    <t>Validate signup with duplicate email restriction</t>
+  </si>
+  <si>
+    <t>Error message: "Email address already registered." displays</t>
+  </si>
+  <si>
     <t>0.49s</t>
   </si>
   <si>
-    <t>TC-SEL-04</t>
-  </si>
-  <si>
-    <t>Validate signup with duplicate email restriction</t>
-  </si>
-  <si>
-    <t>Error message: "Email address already registered." displays</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
     <t>TC-SEL-05</t>
   </si>
   <si>
@@ -148,7 +148,7 @@
     <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
   </si>
   <si>
-    <t>0.66s</t>
+    <t>0.72s</t>
   </si>
   <si>
     <t>TC-SEL-06</t>
@@ -160,159 +160,159 @@
     <t>Form prevents submission or displays missing fields prompt</t>
   </si>
   <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEL-07</t>
+  </si>
+  <si>
+    <t>Validate login password length boundaries</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
+    <t>0.03s</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.06s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>0.58s</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEL-17</t>
+  </si>
+  <si>
+    <t>Verify add expense outflow category transaction successfully updates calculations</t>
+  </si>
+  <si>
+    <t>Outflow transaction decreases net balance</t>
+  </si>
+  <si>
+    <t>0.54s</t>
+  </si>
+  <si>
+    <t>TC-SEL-18</t>
+  </si>
+  <si>
+    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
+  </si>
+  <si>
+    <t>Negative or text values in amount are rejected</t>
+  </si>
+  <si>
+    <t>0.07s</t>
+  </si>
+  <si>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
     <t>0.18s</t>
   </si>
   <si>
-    <t>TC-SEL-07</t>
-  </si>
-  <si>
-    <t>Validate login password length boundaries</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
-  </si>
-  <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.02s</t>
-  </si>
-  <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
-  </si>
-  <si>
-    <t>0.05s</t>
-  </si>
-  <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>0.77s</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEL-17</t>
-  </si>
-  <si>
-    <t>Verify add expense outflow category transaction successfully updates calculations</t>
-  </si>
-  <si>
-    <t>Outflow transaction decreases net balance</t>
-  </si>
-  <si>
-    <t>0.52s</t>
-  </si>
-  <si>
-    <t>TC-SEL-18</t>
-  </si>
-  <si>
-    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
-  </si>
-  <si>
-    <t>Negative or text values in amount are rejected</t>
-  </si>
-  <si>
-    <t>0.07s</t>
-  </si>
-  <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
     <t>TC-SEL-20</t>
   </si>
   <si>
@@ -322,9 +322,6 @@
     <t>Category caps limits are saved and progress bars render</t>
   </si>
   <si>
-    <t>0.37s</t>
-  </si>
-  <si>
     <t>TC-SEL-21</t>
   </si>
   <si>
@@ -334,7 +331,7 @@
     <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
   </si>
   <si>
-    <t>0.72s</t>
+    <t>0.80s</t>
   </si>
   <si>
     <t>TC-SEL-22</t>
@@ -346,6 +343,9 @@
     <t>Updating limit increases budget cap and progress decreases</t>
   </si>
   <si>
+    <t>0.29s</t>
+  </si>
+  <si>
     <t>TC-SEL-23</t>
   </si>
   <si>
@@ -355,7 +355,7 @@
     <t>Monthly Balance Trend line container is visible on page</t>
   </si>
   <si>
-    <t>0.09s</t>
+    <t>0.10s</t>
   </si>
   <si>
     <t>TC-SEL-24</t>
@@ -376,42 +376,45 @@
     <t>Clicking export initializes simulated raw CSV download</t>
   </si>
   <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEL-26</t>
+  </si>
+  <si>
+    <t>Verify user profile metadata fields update successfully</t>
+  </si>
+  <si>
+    <t>Display name successfully updates and synchronizes with sidebar user block</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEL-27</t>
+  </si>
+  <si>
+    <t>Verify preferred default currency synchronization on profile updates</t>
+  </si>
+  <si>
+    <t>Changing currency symbol on profile alters dashboard symbols</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEL-28</t>
+  </si>
+  <si>
+    <t>Verify profile assigned application role is readonly configuration</t>
+  </si>
+  <si>
+    <t>Application role text box contains "readonly" property attribute</t>
+  </si>
+  <si>
     <t>0.11s</t>
   </si>
   <si>
-    <t>TC-SEL-26</t>
-  </si>
-  <si>
-    <t>Verify user profile metadata fields update successfully</t>
-  </si>
-  <si>
-    <t>Display name successfully updates and synchronizes with sidebar user block</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEL-27</t>
-  </si>
-  <si>
-    <t>Verify preferred default currency synchronization on profile updates</t>
-  </si>
-  <si>
-    <t>Changing currency symbol on profile alters dashboard symbols</t>
-  </si>
-  <si>
-    <t>TC-SEL-28</t>
-  </si>
-  <si>
-    <t>Verify profile assigned application role is readonly configuration</t>
-  </si>
-  <si>
-    <t>Application role text box contains "readonly" property attribute</t>
-  </si>
-  <si>
-    <t>0.10s</t>
-  </si>
-  <si>
     <t>TC-SEL-29</t>
   </si>
   <si>
@@ -427,7 +430,7 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>10.20s</t>
+    <t>10.21s</t>
   </si>
   <si>
     <t>TC-SEL-30</t>
@@ -1760,21 +1763,21 @@
         <v>27</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>26</v>
@@ -1783,7 +1786,7 @@
         <v>27</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2036,53 +2039,53 @@
         <v>27</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2197,21 +2200,21 @@
         <v>27</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>26</v>
@@ -2220,53 +2223,53 @@
         <v>27</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2312,16 +2315,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>26</v>
@@ -2330,21 +2333,21 @@
         <v>27</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>26</v>
@@ -2353,21 +2356,21 @@
         <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>26</v>
@@ -2376,21 +2379,21 @@
         <v>27</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>26</v>
@@ -2399,21 +2402,21 @@
         <v>27</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>26</v>
@@ -2422,21 +2425,21 @@
         <v>27</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>26</v>
@@ -2445,21 +2448,21 @@
         <v>27</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>26</v>
@@ -2468,21 +2471,21 @@
         <v>27</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>26</v>
@@ -2491,21 +2494,21 @@
         <v>27</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>26</v>
@@ -2514,21 +2517,21 @@
         <v>27</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>26</v>
@@ -2537,21 +2540,21 @@
         <v>27</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>26</v>
@@ -2560,21 +2563,21 @@
         <v>27</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>26</v>
@@ -2583,21 +2586,21 @@
         <v>27</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>26</v>
@@ -2606,21 +2609,21 @@
         <v>27</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>26</v>
@@ -2629,21 +2632,21 @@
         <v>27</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>26</v>
@@ -2652,21 +2655,21 @@
         <v>27</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>26</v>
@@ -2675,21 +2678,21 @@
         <v>27</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>26</v>
@@ -2698,21 +2701,21 @@
         <v>27</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>26</v>
@@ -2721,21 +2724,21 @@
         <v>27</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>26</v>
@@ -2744,21 +2747,21 @@
         <v>27</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>26</v>
@@ -2767,21 +2770,21 @@
         <v>27</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>26</v>
@@ -2790,21 +2793,21 @@
         <v>27</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>26</v>
@@ -2813,21 +2816,21 @@
         <v>27</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>26</v>
@@ -2836,21 +2839,21 @@
         <v>27</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>26</v>
@@ -2859,21 +2862,21 @@
         <v>27</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>26</v>
@@ -2882,21 +2885,21 @@
         <v>27</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>26</v>
@@ -2905,21 +2908,21 @@
         <v>27</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>26</v>
@@ -2928,21 +2931,21 @@
         <v>27</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>26</v>
@@ -2951,21 +2954,21 @@
         <v>27</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>26</v>
@@ -2974,30 +2977,30 @@
         <v>27</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3043,16 +3046,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>26</v>
@@ -3061,21 +3064,21 @@
         <v>27</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>26</v>
@@ -3084,21 +3087,21 @@
         <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>26</v>
@@ -3107,21 +3110,21 @@
         <v>27</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>26</v>
@@ -3130,21 +3133,21 @@
         <v>27</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>26</v>
@@ -3153,21 +3156,21 @@
         <v>27</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>26</v>
@@ -3176,21 +3179,21 @@
         <v>27</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>26</v>
@@ -3199,21 +3202,21 @@
         <v>27</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>26</v>
@@ -3222,21 +3225,21 @@
         <v>27</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>26</v>
@@ -3245,21 +3248,21 @@
         <v>27</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>26</v>
@@ -3268,21 +3271,21 @@
         <v>27</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>26</v>
@@ -3291,21 +3294,21 @@
         <v>27</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>26</v>
@@ -3314,21 +3317,21 @@
         <v>27</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>26</v>
@@ -3337,21 +3340,21 @@
         <v>27</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>26</v>
@@ -3360,21 +3363,21 @@
         <v>27</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>26</v>
@@ -3383,21 +3386,21 @@
         <v>27</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>26</v>
@@ -3406,21 +3409,21 @@
         <v>27</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>26</v>
@@ -3429,21 +3432,21 @@
         <v>27</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>26</v>
@@ -3452,21 +3455,21 @@
         <v>27</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>26</v>
@@ -3475,21 +3478,21 @@
         <v>27</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>26</v>
@@ -3498,21 +3501,21 @@
         <v>27</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>26</v>
@@ -3521,21 +3524,21 @@
         <v>27</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>26</v>
@@ -3544,21 +3547,21 @@
         <v>27</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>26</v>
@@ -3567,21 +3570,21 @@
         <v>27</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>26</v>
@@ -3590,21 +3593,21 @@
         <v>27</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>26</v>
@@ -3613,21 +3616,21 @@
         <v>27</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>26</v>
@@ -3636,21 +3639,21 @@
         <v>27</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>26</v>
@@ -3659,21 +3662,21 @@
         <v>27</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>26</v>
@@ -3682,21 +3685,21 @@
         <v>27</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>26</v>
@@ -3705,30 +3708,30 @@
         <v>27</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Master_Report.xlsx
+++ b/reports/Master_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="495">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:07 AM</t>
+    <t>6/16/2026, 5:20:48 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>6.93s</t>
+    <t>28.65s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,708 +103,768 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.80s</t>
+  </si>
+  <si>
+    <t>TC-SEL-02</t>
+  </si>
+  <si>
+    <t>Validate password mismatch constraint</t>
+  </si>
+  <si>
+    <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
+  </si>
+  <si>
+    <t>0.66s</t>
+  </si>
+  <si>
+    <t>TC-SEL-03</t>
+  </si>
+  <si>
+    <t>Validate password minimum length validation constraint</t>
+  </si>
+  <si>
+    <t>Error message: "Password must be at least 8 characters." displays</t>
+  </si>
+  <si>
+    <t>0.49s</t>
+  </si>
+  <si>
+    <t>TC-SEL-04</t>
+  </si>
+  <si>
+    <t>Validate signup with duplicate email restriction</t>
+  </si>
+  <si>
+    <t>Error message: "Email address already registered." displays</t>
+  </si>
+  <si>
+    <t>0.58s</t>
+  </si>
+  <si>
+    <t>TC-SEL-05</t>
+  </si>
+  <si>
+    <t>Verify successful user signup and redirect to main Dashboard view</t>
+  </si>
+  <si>
+    <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
+  </si>
+  <si>
+    <t>0.85s</t>
+  </si>
+  <si>
+    <t>TC-SEL-06</t>
+  </si>
+  <si>
+    <t>Validate login empty fields boundary rules</t>
+  </si>
+  <si>
+    <t>Form prevents submission or displays missing fields prompt</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEL-07</t>
+  </si>
+  <si>
+    <t>Validate login password length boundaries</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.06s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>0.57s</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEL-17</t>
+  </si>
+  <si>
+    <t>Verify add expense outflow category transaction successfully updates calculations</t>
+  </si>
+  <si>
+    <t>Outflow transaction decreases net balance</t>
+  </si>
+  <si>
+    <t>0.51s</t>
+  </si>
+  <si>
+    <t>TC-SEL-18</t>
+  </si>
+  <si>
+    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
+  </si>
+  <si>
+    <t>Negative or text values in amount are rejected</t>
+  </si>
+  <si>
+    <t>0.07s</t>
+  </si>
+  <si>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-SEL-20</t>
+  </si>
+  <si>
+    <t>Verify category budget cap limit configuration successfully saves limiters</t>
+  </si>
+  <si>
+    <t>Category caps limits are saved and progress bars render</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEL-21</t>
+  </si>
+  <si>
+    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
+  </si>
+  <si>
+    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
+  </si>
+  <si>
+    <t>0.79s</t>
+  </si>
+  <si>
+    <t>TC-SEL-22</t>
+  </si>
+  <si>
+    <t>Verify edit category budget limit increases active threshold</t>
+  </si>
+  <si>
+    <t>Updating limit increases budget cap and progress decreases</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEL-23</t>
+  </si>
+  <si>
+    <t>Verify reports dashboard trend chart elements rendering</t>
+  </si>
+  <si>
+    <t>Monthly Balance Trend line container is visible on page</t>
+  </si>
+  <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>TC-SEL-24</t>
+  </si>
+  <si>
+    <t>Verify category distribution breakdown list aggregates metrics</t>
+  </si>
+  <si>
+    <t>Analytics categories breakdown table loads and sums values</t>
+  </si>
+  <si>
+    <t>TC-SEL-25</t>
+  </si>
+  <si>
+    <t>Verify raw data export reports CSV simulation download trigger</t>
+  </si>
+  <si>
+    <t>Clicking export initializes simulated raw CSV download</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-SEL-26</t>
+  </si>
+  <si>
+    <t>Verify user profile metadata fields update successfully</t>
+  </si>
+  <si>
+    <t>Display name successfully updates and synchronizes with sidebar user block</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEL-27</t>
+  </si>
+  <si>
+    <t>Verify preferred default currency synchronization on profile updates</t>
+  </si>
+  <si>
+    <t>Changing currency symbol on profile alters dashboard symbols</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEL-28</t>
+  </si>
+  <si>
+    <t>Verify profile assigned application role is readonly configuration</t>
+  </si>
+  <si>
+    <t>Application role text box contains "readonly" property attribute</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEL-29</t>
+  </si>
+  <si>
+    <t>Verify successful user logout redirects to authentication login view</t>
+  </si>
+  <si>
+    <t>Session clears and client redirects to login view immediately</t>
+  </si>
+  <si>
+    <t>0.09s</t>
+  </si>
+  <si>
+    <t>TC-SEL-30</t>
+  </si>
+  <si>
+    <t>Verify inactive session security timeout auto-redirect functionality</t>
+  </si>
+  <si>
+    <t>Inactivity trigger automatically destroys token and redirects to login view</t>
+  </si>
+  <si>
+    <t>TC-SEC-01</t>
+  </si>
+  <si>
+    <t>Security Vulnerability Testing Suite</t>
+  </si>
+  <si>
+    <t>TC-SEC-01: Login Email input field sanitization check against standard SQL injection patterns</t>
+  </si>
+  <si>
+    <t>Application sanitizes input or safely handles single quote sequences</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEC-02</t>
+  </si>
+  <si>
+    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
+  </si>
+  <si>
+    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
     <t>0.34s</t>
   </si>
   <si>
-    <t>TC-SEL-02</t>
-  </si>
-  <si>
-    <t>Validate password mismatch constraint</t>
-  </si>
-  <si>
-    <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEL-03</t>
-  </si>
-  <si>
-    <t>Validate password minimum length validation constraint</t>
-  </si>
-  <si>
-    <t>Error message: "Password must be at least 8 characters." displays</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEL-04</t>
-  </si>
-  <si>
-    <t>Validate signup with duplicate email restriction</t>
-  </si>
-  <si>
-    <t>Error message: "Email address already registered." displays</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEL-05</t>
-  </si>
-  <si>
-    <t>Verify successful user signup and redirect to main Dashboard view</t>
-  </si>
-  <si>
-    <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-SEL-06</t>
-  </si>
-  <si>
-    <t>Validate login empty fields boundary rules</t>
-  </si>
-  <si>
-    <t>Form prevents submission or displays missing fields prompt</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEL-07</t>
-  </si>
-  <si>
-    <t>Validate login password length boundaries</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-SEC-28</t>
+  </si>
+  <si>
+    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
+  </si>
+  <si>
+    <t>Improperly formatted Authorization header formats fail schema checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-29</t>
+  </si>
+  <si>
+    <t>TC-SEC-29: Access-Control-Allow-Origin wildcard denial for credentialed cross-origin requests</t>
+  </si>
+  <si>
+    <t>Server restricts CORS credentials access when wildcard is used</t>
+  </si>
+  <si>
+    <t>TC-SEC-30</t>
+  </si>
+  <si>
+    <t>TC-SEC-30: Verify CORS preflight headers Access-Control-Allow-Origin checks on sensitive endpoints</t>
+  </si>
+  <si>
+    <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
+  </si>
+  <si>
+    <t>TC-APP-01</t>
+  </si>
+  <si>
+    <t>Appium Mobile E2E Suite</t>
+  </si>
+  <si>
+    <t>TC-APP-01: Verify valid mobile user login credentials submission and workspace routing</t>
+  </si>
+  <si>
+    <t>Mobile app logs in and loads dashboard header widget</t>
+  </si>
+  <si>
+    <t>TC-APP-02</t>
+  </si>
+  <si>
+    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
+  </si>
+  <si>
+    <t>App prevents submission on empty email or password fields</t>
+  </si>
+  <si>
+    <t>TC-APP-03</t>
+  </si>
+  <si>
+    <t>TC-APP-03: Validate login email address format checking rules</t>
+  </si>
+  <si>
+    <t>Error label displays when email format is invalid</t>
+  </si>
+  <si>
+    <t>TC-APP-04</t>
+  </si>
+  <si>
+    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
+  </si>
+  <si>
+    <t>App registers biometric device setup option in local state</t>
+  </si>
+  <si>
+    <t>TC-APP-05</t>
+  </si>
+  <si>
+    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
+  </si>
+  <si>
+    <t>Dashboard balance, income, and expense summary widgets render</t>
+  </si>
+  <si>
+    <t>TC-APP-06</t>
+  </si>
+  <si>
+    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
+  </si>
+  <si>
+    <t>Balance summary card resolves within view limits</t>
+  </si>
+  <si>
+    <t>TC-APP-07</t>
+  </si>
+  <si>
+    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
+  </si>
+  <si>
+    <t>Pull to refresh updates transaction listings from background storage</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-APP-08</t>
+  </si>
+  <si>
+    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
+  </si>
+  <si>
+    <t>Income sheet modal slides into view</t>
+  </si>
+  <si>
+    <t>TC-APP-09</t>
+  </si>
+  <si>
+    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
+  </si>
+  <si>
+    <t>Category select holds Salary, Freelance, and Investments options</t>
+  </si>
+  <si>
+    <t>TC-APP-10</t>
+  </si>
+  <si>
+    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
+  </si>
+  <si>
+    <t>Income fields accept numeric and descriptive inputs</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-APP-11</t>
+  </si>
+  <si>
+    <t>TC-APP-11: Validate empty income form submission error indicators</t>
+  </si>
+  <si>
+    <t>Missing amount triggers mobile error highlights</t>
   </si>
   <si>
     <t>0.21s</t>
   </si>
   <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.02s</t>
-  </si>
-  <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
-  </si>
-  <si>
-    <t>0.05s</t>
-  </si>
-  <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
-  </si>
-  <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEL-17</t>
-  </si>
-  <si>
-    <t>Verify add expense outflow category transaction successfully updates calculations</t>
-  </si>
-  <si>
-    <t>Outflow transaction decreases net balance</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEL-18</t>
-  </si>
-  <si>
-    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
-  </si>
-  <si>
-    <t>Negative or text values in amount are rejected</t>
-  </si>
-  <si>
-    <t>0.06s</t>
-  </si>
-  <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>TC-SEL-20</t>
-  </si>
-  <si>
-    <t>Verify category budget cap limit configuration successfully saves limiters</t>
-  </si>
-  <si>
-    <t>Category caps limits are saved and progress bars render</t>
-  </si>
-  <si>
-    <t>TC-SEL-21</t>
-  </si>
-  <si>
-    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
-  </si>
-  <si>
-    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
-  </si>
-  <si>
-    <t>0.68s</t>
-  </si>
-  <si>
-    <t>TC-SEL-22</t>
-  </si>
-  <si>
-    <t>Verify edit category budget limit increases active threshold</t>
-  </si>
-  <si>
-    <t>Updating limit increases budget cap and progress decreases</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEL-23</t>
-  </si>
-  <si>
-    <t>Verify reports dashboard trend chart elements rendering</t>
-  </si>
-  <si>
-    <t>Monthly Balance Trend line container is visible on page</t>
-  </si>
-  <si>
-    <t>TC-SEL-24</t>
-  </si>
-  <si>
-    <t>Verify category distribution breakdown list aggregates metrics</t>
-  </si>
-  <si>
-    <t>Analytics categories breakdown table loads and sums values</t>
-  </si>
-  <si>
-    <t>0.08s</t>
-  </si>
-  <si>
-    <t>TC-SEL-25</t>
-  </si>
-  <si>
-    <t>Verify raw data export reports CSV simulation download trigger</t>
-  </si>
-  <si>
-    <t>Clicking export initializes simulated raw CSV download</t>
-  </si>
-  <si>
-    <t>0.07s</t>
-  </si>
-  <si>
-    <t>TC-SEL-26</t>
-  </si>
-  <si>
-    <t>Verify user profile metadata fields update successfully</t>
-  </si>
-  <si>
-    <t>Display name successfully updates and synchronizes with sidebar user block</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEL-27</t>
-  </si>
-  <si>
-    <t>Verify preferred default currency synchronization on profile updates</t>
-  </si>
-  <si>
-    <t>Changing currency symbol on profile alters dashboard symbols</t>
-  </si>
-  <si>
-    <t>TC-SEL-28</t>
-  </si>
-  <si>
-    <t>Verify profile assigned application role is readonly configuration</t>
-  </si>
-  <si>
-    <t>Application role text box contains "readonly" property attribute</t>
-  </si>
-  <si>
-    <t>0.09s</t>
-  </si>
-  <si>
-    <t>TC-SEL-29</t>
-  </si>
-  <si>
-    <t>Verify successful user logout redirects to authentication login view</t>
-  </si>
-  <si>
-    <t>Session clears and client redirects to login view immediately</t>
-  </si>
-  <si>
-    <t>TC-SEL-30</t>
-  </si>
-  <si>
-    <t>Verify inactive session security timeout auto-redirect functionality</t>
-  </si>
-  <si>
-    <t>Inactivity trigger automatically destroys token and redirects to login view</t>
-  </si>
-  <si>
-    <t>0.00s</t>
-  </si>
-  <si>
-    <t>TC-SEC-01</t>
-  </si>
-  <si>
-    <t>Security Vulnerability Testing Suite</t>
-  </si>
-  <si>
-    <t>TC-SEC-01: Login Email input field sanitization check against standard SQL injection patterns</t>
-  </si>
-  <si>
-    <t>Application sanitizes input or safely handles single quote sequences</t>
-  </si>
-  <si>
-    <t>TC-SEC-02</t>
-  </si>
-  <si>
-    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
-  </si>
-  <si>
-    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>TC-SEC-28</t>
-  </si>
-  <si>
-    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
-  </si>
-  <si>
-    <t>Improperly formatted Authorization header formats fail schema checks</t>
-  </si>
-  <si>
-    <t>TC-SEC-29</t>
-  </si>
-  <si>
-    <t>TC-SEC-29: Access-Control-Allow-Origin wildcard denial for credentialed cross-origin requests</t>
-  </si>
-  <si>
-    <t>Server restricts CORS credentials access when wildcard is used</t>
-  </si>
-  <si>
-    <t>TC-SEC-30</t>
-  </si>
-  <si>
-    <t>TC-SEC-30: Verify CORS preflight headers Access-Control-Allow-Origin checks on sensitive endpoints</t>
-  </si>
-  <si>
-    <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
-  </si>
-  <si>
-    <t>TC-APP-01</t>
-  </si>
-  <si>
-    <t>Appium Mobile E2E Suite</t>
-  </si>
-  <si>
-    <t>TC-APP-01: Verify valid mobile user login credentials submission and workspace routing</t>
-  </si>
-  <si>
-    <t>Mobile app logs in and loads dashboard header widget</t>
-  </si>
-  <si>
-    <t>TC-APP-02</t>
-  </si>
-  <si>
-    <t>TC-APP-02: Validate login validation empty fields boundary constraints</t>
-  </si>
-  <si>
-    <t>App prevents submission on empty email or password fields</t>
-  </si>
-  <si>
-    <t>TC-APP-03</t>
-  </si>
-  <si>
-    <t>TC-APP-03: Validate login email address format checking rules</t>
-  </si>
-  <si>
-    <t>Error label displays when email format is invalid</t>
-  </si>
-  <si>
-    <t>TC-APP-04</t>
-  </si>
-  <si>
-    <t>TC-APP-04: Verify biometric fingerprint touch ID authorization setups prompt</t>
-  </si>
-  <si>
-    <t>App registers biometric device setup option in local state</t>
-  </si>
-  <si>
-    <t>TC-APP-05</t>
-  </si>
-  <si>
-    <t>TC-APP-05: Verify mobile dashboard layout rendering and stats cards visibility</t>
-  </si>
-  <si>
-    <t>Dashboard balance, income, and expense summary widgets render</t>
-  </si>
-  <si>
-    <t>TC-APP-06</t>
-  </si>
-  <si>
-    <t>TC-APP-06: Verify balance summary panels alignment and scroll constraints</t>
-  </si>
-  <si>
-    <t>Balance summary card resolves within view limits</t>
-  </si>
-  <si>
-    <t>TC-APP-07</t>
-  </si>
-  <si>
-    <t>TC-APP-07: Verify vertical swipe gesture triggers pull-to-refresh data sync</t>
-  </si>
-  <si>
-    <t>Pull to refresh updates transaction listings from background storage</t>
-  </si>
-  <si>
-    <t>TC-APP-08</t>
-  </si>
-  <si>
-    <t>TC-APP-08: Verify opening Add Income bottom sheet interface component</t>
-  </si>
-  <si>
-    <t>Income sheet modal slides into view</t>
-  </si>
-  <si>
-    <t>TC-APP-09</t>
-  </si>
-  <si>
-    <t>TC-APP-09: Verify add income transaction category selection drop-down items</t>
-  </si>
-  <si>
-    <t>Category select holds Salary, Freelance, and Investments options</t>
-  </si>
-  <si>
-    <t>TC-APP-10</t>
-  </si>
-  <si>
-    <t>TC-APP-10: Verify inflow amount and source description input validation checks</t>
-  </si>
-  <si>
-    <t>Income fields accept numeric and descriptive inputs</t>
-  </si>
-  <si>
-    <t>TC-APP-11</t>
-  </si>
-  <si>
-    <t>TC-APP-11: Validate empty income form submission error indicators</t>
-  </si>
-  <si>
-    <t>Missing amount triggers mobile error highlights</t>
-  </si>
-  <si>
     <t>TC-APP-12</t>
   </si>
   <si>
@@ -832,6 +892,9 @@
     <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
   </si>
   <si>
+    <t>0.33s</t>
+  </si>
+  <si>
     <t>TC-APP-15</t>
   </si>
   <si>
@@ -859,6 +922,9 @@
     <t>Progress bar limits adjust to new budget configurations</t>
   </si>
   <si>
+    <t>0.39s</t>
+  </si>
+  <si>
     <t>TC-APP-18</t>
   </si>
   <si>
@@ -1000,91 +1066,211 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:00 AM</t>
+    <t>6/16/2026, 5:20:36 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
   </si>
   <si>
+    <t>Click Register Here link</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>RegisterPage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter register name: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entered: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter register email: </t>
+  </si>
+  <si>
+    <t>Enter register password</t>
+  </si>
+  <si>
+    <t>Confirm register password</t>
+  </si>
+  <si>
+    <t>Click Sign Up Button</t>
+  </si>
+  <si>
+    <t>Get registration error message</t>
+  </si>
+  <si>
+    <t>Text found: "All fields are required for registration."</t>
+  </si>
+  <si>
+    <t>Enter register name: Sarah Connor</t>
+  </si>
+  <si>
+    <t>Entered: Sarah Connor</t>
+  </si>
+  <si>
+    <t>Enter register email: sarah@budget.com</t>
+  </si>
+  <si>
+    <t>Entered: sarah@budget.com</t>
+  </si>
+  <si>
+    <t>Entered: SecurePass123!</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:37 AM</t>
+  </si>
+  <si>
+    <t>Entered: WrongPass123!</t>
+  </si>
+  <si>
+    <t>Text found: "Passwords do not match."</t>
+  </si>
+  <si>
+    <t>Entered: 12345</t>
+  </si>
+  <si>
+    <t>Text found: "Password must be at least 8 characters."</t>
+  </si>
+  <si>
+    <t>Enter register name: Admin User</t>
+  </si>
+  <si>
+    <t>Entered: Admin User</t>
+  </si>
+  <si>
+    <t>Enter register email: admin@budget.com</t>
+  </si>
+  <si>
+    <t>Entered: admin@budget.com</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:38 AM</t>
+  </si>
+  <si>
+    <t>Entered: SmartBudgetPass123!</t>
+  </si>
+  <si>
+    <t>Text found: "Email address already registered."</t>
+  </si>
+  <si>
+    <t>Entered: SarahPass123!</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:39 AM</t>
+  </si>
+  <si>
+    <t>DashboardPage</t>
+  </si>
+  <si>
+    <t>Click Logout Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter login email: </t>
+  </si>
+  <si>
+    <t>Enter login password</t>
+  </si>
+  <si>
+    <t>Click Sign In Button</t>
+  </si>
+  <si>
+    <t>Get login error validation text</t>
+  </si>
+  <si>
+    <t>Text found: ""</t>
+  </si>
+  <si>
+    <t>Enter login email: user@budget.com</t>
+  </si>
+  <si>
+    <t>Entered: user@budget.com</t>
+  </si>
+  <si>
+    <t>Entered: 123</t>
+  </si>
+  <si>
     <t>Enter login email: admin@budget.com</t>
   </si>
   <si>
-    <t>Entered: admin@budget.com</t>
-  </si>
-  <si>
-    <t>Enter login password</t>
-  </si>
-  <si>
-    <t>Entered: SmartBudgetPass123!</t>
-  </si>
-  <si>
-    <t>Click Sign In Button</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>DashboardPage</t>
-  </si>
-  <si>
-    <t>Click Logout Button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter login email: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entered: </t>
-  </si>
-  <si>
-    <t>Get login error validation text</t>
-  </si>
-  <si>
-    <t>Text found (Simulated): "Validation error: Fields required"</t>
-  </si>
-  <si>
-    <t>Enter login email: invalidemail</t>
-  </si>
-  <si>
-    <t>Entered: invalidemail</t>
-  </si>
-  <si>
-    <t>Entered: Pass123!</t>
-  </si>
-  <si>
-    <t>Text found (Simulated): "Invalid email or password credential."</t>
-  </si>
-  <si>
-    <t>Scroll down</t>
+    <t>Text found: "Invalid email or password credential."</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:40 AM</t>
+  </si>
+  <si>
+    <t>Check Remember Me option</t>
+  </si>
+  <si>
+    <t>Read total balance statistic</t>
+  </si>
+  <si>
+    <t>Text found: "$3,410.00"</t>
+  </si>
+  <si>
+    <t>Read total income statistic</t>
+  </si>
+  <si>
+    <t>Text found: "$5,000.00"</t>
+  </si>
+  <si>
+    <t>Read total expense statistic</t>
+  </si>
+  <si>
+    <t>Text found: "$1,590.00"</t>
+  </si>
+  <si>
+    <t>Type query "Rent"</t>
+  </si>
+  <si>
+    <t>Entered: Rent</t>
+  </si>
+  <si>
+    <t>Clear query</t>
   </si>
   <si>
     <t>Navigate to tab: nav-income</t>
   </si>
   <si>
+    <t>6/16/2026, 5:20:41 AM</t>
+  </si>
+  <si>
     <t>Select income category: Salary</t>
   </si>
   <si>
     <t>Entered: Salary</t>
   </si>
   <si>
-    <t>Enter income amount: 4000</t>
-  </si>
-  <si>
-    <t>Entered: 4000</t>
-  </si>
-  <si>
-    <t>Enter income description: Company salary</t>
-  </si>
-  <si>
-    <t>Entered: Company salary</t>
+    <t>Enter income amount: 2500</t>
+  </si>
+  <si>
+    <t>Entered: 2500</t>
+  </si>
+  <si>
+    <t>Enter income description: Part-time consultancy paycheck</t>
+  </si>
+  <si>
+    <t>Entered: Part-time consultancy paycheck</t>
   </si>
   <si>
     <t>Click Log Income Submit button</t>
   </si>
   <si>
-    <t>Read total balance statistic</t>
-  </si>
-  <si>
-    <t>Text found (Simulated): "Dashboard"</t>
+    <t>Text found: "$5,910.00"</t>
+  </si>
+  <si>
+    <t>Click submit button on empty form</t>
+  </si>
+  <si>
+    <t>Navigate to tab: nav-dashboard</t>
+  </si>
+  <si>
+    <t>Click first delete button</t>
+  </si>
+  <si>
+    <t>Text found: "$910.00"</t>
   </si>
   <si>
     <t>Navigate to tab: nav-expense</t>
@@ -1096,271 +1282,46 @@
     <t>Entered: Food</t>
   </si>
   <si>
-    <t>Enter expense amount: 150</t>
-  </si>
-  <si>
-    <t>Entered: 150</t>
-  </si>
-  <si>
-    <t>Enter expense description: Groceries</t>
-  </si>
-  <si>
-    <t>Entered: Groceries</t>
+    <t>6/16/2026, 5:20:42 AM</t>
+  </si>
+  <si>
+    <t>Enter expense amount: 120</t>
+  </si>
+  <si>
+    <t>Entered: 120</t>
+  </si>
+  <si>
+    <t>Enter expense description: Weekly grocery run</t>
+  </si>
+  <si>
+    <t>Entered: Weekly grocery run</t>
   </si>
   <si>
     <t>Click Log Expense Submit button</t>
   </si>
   <si>
+    <t>Text found: "$790.00"</t>
+  </si>
+  <si>
+    <t>Delete first expense transaction</t>
+  </si>
+  <si>
+    <t>Text found: "$1,990.00"</t>
+  </si>
+  <si>
     <t>Navigate to tab: nav-budget</t>
   </si>
   <si>
     <t>Select budget segment: Food</t>
   </si>
   <si>
-    <t>Enter budget cap limit: 700</t>
-  </si>
-  <si>
-    <t>Entered: 700</t>
+    <t>Enter budget cap limit: 600</t>
+  </si>
+  <si>
+    <t>Entered: 600</t>
   </si>
   <si>
     <t>Click Save Budget Allocation button</t>
-  </si>
-  <si>
-    <t>Get text</t>
-  </si>
-  <si>
-    <t>Select budget segment: Shopping</t>
-  </si>
-  <si>
-    <t>Entered: Shopping</t>
-  </si>
-  <si>
-    <t>Enter budget cap limit: 100</t>
-  </si>
-  <si>
-    <t>Entered: 100</t>
-  </si>
-  <si>
-    <t>Select expense category: Shopping</t>
-  </si>
-  <si>
-    <t>Enter expense amount: 120</t>
-  </si>
-  <si>
-    <t>Entered: 120</t>
-  </si>
-  <si>
-    <t>Enter expense description: New shirt</t>
-  </si>
-  <si>
-    <t>Entered: New shirt</t>
-  </si>
-  <si>
-    <t>Acknowledge budget cap warning dialog</t>
-  </si>
-  <si>
-    <t>Navigate to tab: nav-profile</t>
-  </si>
-  <si>
-    <t>Enter profile name: Alice Margatroid</t>
-  </si>
-  <si>
-    <t>Entered: Alice Margatroid</t>
-  </si>
-  <si>
-    <t>Select currency: $</t>
-  </si>
-  <si>
-    <t>Entered: $</t>
-  </si>
-  <si>
-    <t>Click Save Profile Settings button</t>
-  </si>
-  <si>
-    <t>Read profile update success banner</t>
-  </si>
-  <si>
-    <t>Text found (Simulated): "Profile settings updated successfully!"</t>
-  </si>
-  <si>
-    <t>Select currency: €</t>
-  </si>
-  <si>
-    <t>Entered: €</t>
-  </si>
-  <si>
-    <t>Click Register Here link</t>
-  </si>
-  <si>
-    <t>RegisterPage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter register name: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter register email: </t>
-  </si>
-  <si>
-    <t>Enter register password</t>
-  </si>
-  <si>
-    <t>Confirm register password</t>
-  </si>
-  <si>
-    <t>Click Sign Up Button</t>
-  </si>
-  <si>
-    <t>Get registration error message</t>
-  </si>
-  <si>
-    <t>Text found: "All fields are required for registration."</t>
-  </si>
-  <si>
-    <t>Enter register name: Sarah Connor</t>
-  </si>
-  <si>
-    <t>Entered: Sarah Connor</t>
-  </si>
-  <si>
-    <t>Enter register email: sarah@budget.com</t>
-  </si>
-  <si>
-    <t>Entered: sarah@budget.com</t>
-  </si>
-  <si>
-    <t>Entered: SecurePass123!</t>
-  </si>
-  <si>
-    <t>6/16/2026, 4:44:01 AM</t>
-  </si>
-  <si>
-    <t>Entered: WrongPass123!</t>
-  </si>
-  <si>
-    <t>Text found: "Passwords do not match."</t>
-  </si>
-  <si>
-    <t>Entered: 12345</t>
-  </si>
-  <si>
-    <t>Text found: "Password must be at least 8 characters."</t>
-  </si>
-  <si>
-    <t>Enter register name: Admin User</t>
-  </si>
-  <si>
-    <t>Entered: Admin User</t>
-  </si>
-  <si>
-    <t>Enter register email: admin@budget.com</t>
-  </si>
-  <si>
-    <t>Text found: "Email address already registered."</t>
-  </si>
-  <si>
-    <t>6/16/2026, 4:44:02 AM</t>
-  </si>
-  <si>
-    <t>Entered: SarahPass123!</t>
-  </si>
-  <si>
-    <t>Text found: ""</t>
-  </si>
-  <si>
-    <t>Enter login email: user@budget.com</t>
-  </si>
-  <si>
-    <t>Entered: user@budget.com</t>
-  </si>
-  <si>
-    <t>Entered: 123</t>
-  </si>
-  <si>
-    <t>Text found: "Invalid email or password credential."</t>
-  </si>
-  <si>
-    <t>6/16/2026, 4:44:03 AM</t>
-  </si>
-  <si>
-    <t>Check Remember Me option</t>
-  </si>
-  <si>
-    <t>Text found: "$3,410.00"</t>
-  </si>
-  <si>
-    <t>Read total income statistic</t>
-  </si>
-  <si>
-    <t>Text found: "$5,000.00"</t>
-  </si>
-  <si>
-    <t>Read total expense statistic</t>
-  </si>
-  <si>
-    <t>Text found: "$1,590.00"</t>
-  </si>
-  <si>
-    <t>Type query "Rent"</t>
-  </si>
-  <si>
-    <t>Entered: Rent</t>
-  </si>
-  <si>
-    <t>Clear query</t>
-  </si>
-  <si>
-    <t>Enter income amount: 2500</t>
-  </si>
-  <si>
-    <t>Entered: 2500</t>
-  </si>
-  <si>
-    <t>Enter income description: Part-time consultancy paycheck</t>
-  </si>
-  <si>
-    <t>Entered: Part-time consultancy paycheck</t>
-  </si>
-  <si>
-    <t>6/16/2026, 4:44:04 AM</t>
-  </si>
-  <si>
-    <t>Text found: "$5,910.00"</t>
-  </si>
-  <si>
-    <t>Click submit button on empty form</t>
-  </si>
-  <si>
-    <t>Navigate to tab: nav-dashboard</t>
-  </si>
-  <si>
-    <t>Click first delete button</t>
-  </si>
-  <si>
-    <t>Text found: "$910.00"</t>
-  </si>
-  <si>
-    <t>Enter expense description: Weekly grocery run</t>
-  </si>
-  <si>
-    <t>Entered: Weekly grocery run</t>
-  </si>
-  <si>
-    <t>Text found: "$790.00"</t>
-  </si>
-  <si>
-    <t>Delete first expense transaction</t>
-  </si>
-  <si>
-    <t>Text found: "$1,990.00"</t>
-  </si>
-  <si>
-    <t>6/16/2026, 4:44:05 AM</t>
-  </si>
-  <si>
-    <t>Enter budget cap limit: 600</t>
-  </si>
-  <si>
-    <t>Entered: 600</t>
   </si>
   <si>
     <t>Read budget progress</t>
@@ -1378,12 +1339,24 @@
 $0.00 / $1500.00 (0%)"</t>
   </si>
   <si>
+    <t>6/16/2026, 5:20:43 AM</t>
+  </si>
+  <si>
+    <t>Select budget segment: Shopping</t>
+  </si>
+  <si>
+    <t>Entered: Shopping</t>
+  </si>
+  <si>
     <t>Enter budget cap limit: 200</t>
   </si>
   <si>
     <t>Entered: 200</t>
   </si>
   <si>
+    <t>Select expense category: Shopping</t>
+  </si>
+  <si>
     <t>Enter expense amount: 250</t>
   </si>
   <si>
@@ -1396,13 +1369,16 @@
     <t>Entered: Designer sneakers</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:06 AM</t>
+    <t>Acknowledge budget cap warning dialog</t>
   </si>
   <si>
     <t>Enter budget cap limit: 1000</t>
   </si>
   <si>
     <t>Entered: 1000</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:44 AM</t>
   </si>
   <si>
     <t>Check updated Food cap</t>
@@ -1437,10 +1413,115 @@
     <t>Click Export Raw Data button</t>
   </si>
   <si>
+    <t>Navigate to tab: nav-profile</t>
+  </si>
+  <si>
+    <t>Enter profile name: Alice Margatroid</t>
+  </si>
+  <si>
+    <t>Entered: Alice Margatroid</t>
+  </si>
+  <si>
+    <t>Select currency: $</t>
+  </si>
+  <si>
+    <t>Entered: $</t>
+  </si>
+  <si>
+    <t>Click Save Profile Settings button</t>
+  </si>
+  <si>
+    <t>Read profile update success banner</t>
+  </si>
+  <si>
     <t>Text found: "Profile settings updated successfully!"</t>
   </si>
   <si>
+    <t>Select currency: €</t>
+  </si>
+  <si>
+    <t>Entered: €</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:45 AM</t>
+  </si>
+  <si>
     <t>Text found: "€1,740.00"</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:46 AM</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:47 AM</t>
+  </si>
+  <si>
+    <t>Text found (Simulated): "Validation error: Fields required"</t>
+  </si>
+  <si>
+    <t>Enter login email: invalidemail</t>
+  </si>
+  <si>
+    <t>Entered: invalidemail</t>
+  </si>
+  <si>
+    <t>Entered: Pass123!</t>
+  </si>
+  <si>
+    <t>Text found (Simulated): "Invalid email or password credential."</t>
+  </si>
+  <si>
+    <t>Scroll down</t>
+  </si>
+  <si>
+    <t>Enter income amount: 4000</t>
+  </si>
+  <si>
+    <t>Entered: 4000</t>
+  </si>
+  <si>
+    <t>Enter income description: Company salary</t>
+  </si>
+  <si>
+    <t>Entered: Company salary</t>
+  </si>
+  <si>
+    <t>Text found (Simulated): "Dashboard"</t>
+  </si>
+  <si>
+    <t>Enter expense amount: 150</t>
+  </si>
+  <si>
+    <t>Entered: 150</t>
+  </si>
+  <si>
+    <t>Enter expense description: Groceries</t>
+  </si>
+  <si>
+    <t>Entered: Groceries</t>
+  </si>
+  <si>
+    <t>Enter budget cap limit: 700</t>
+  </si>
+  <si>
+    <t>Entered: 700</t>
+  </si>
+  <si>
+    <t>Get text</t>
+  </si>
+  <si>
+    <t>Enter budget cap limit: 100</t>
+  </si>
+  <si>
+    <t>Entered: 100</t>
+  </si>
+  <si>
+    <t>Enter expense description: New shirt</t>
+  </si>
+  <si>
+    <t>Entered: New shirt</t>
+  </si>
+  <si>
+    <t>Text found (Simulated): "Profile settings updated successfully!"</t>
   </si>
 </sst>
 </file>
@@ -2213,21 +2294,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -2236,21 +2317,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -2259,21 +2340,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -2282,21 +2363,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -2305,21 +2386,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -2328,21 +2409,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -2351,21 +2432,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -2374,21 +2455,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -2397,21 +2478,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -2420,21 +2501,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -2443,21 +2524,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -2466,21 +2547,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -2489,21 +2570,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -2512,21 +2593,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -2535,21 +2616,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -2558,21 +2639,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -2581,21 +2662,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -2604,21 +2685,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -2627,21 +2708,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -2650,21 +2731,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -2673,21 +2754,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -2696,21 +2777,21 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>27</v>
@@ -2719,21 +2800,21 @@
         <v>28</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>27</v>
@@ -2742,21 +2823,21 @@
         <v>28</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>27</v>
@@ -2765,21 +2846,21 @@
         <v>28</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>27</v>
@@ -2788,21 +2869,21 @@
         <v>28</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>27</v>
@@ -2811,21 +2892,21 @@
         <v>28</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>137</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>27</v>
@@ -2834,21 +2915,21 @@
         <v>28</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>27</v>
@@ -2857,21 +2938,21 @@
         <v>28</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>27</v>
@@ -2880,21 +2961,21 @@
         <v>28</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>27</v>
@@ -2903,21 +2984,21 @@
         <v>28</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>27</v>
@@ -2926,21 +3007,21 @@
         <v>28</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>27</v>
@@ -2949,21 +3030,21 @@
         <v>28</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>27</v>
@@ -2972,21 +3053,21 @@
         <v>28</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>27</v>
@@ -2995,21 +3076,21 @@
         <v>28</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>27</v>
@@ -3018,21 +3099,21 @@
         <v>28</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>27</v>
@@ -3041,21 +3122,21 @@
         <v>28</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>27</v>
@@ -3064,21 +3145,21 @@
         <v>28</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>27</v>
@@ -3087,21 +3168,21 @@
         <v>28</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>27</v>
@@ -3110,21 +3191,21 @@
         <v>28</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>27</v>
@@ -3133,21 +3214,21 @@
         <v>28</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>27</v>
@@ -3156,21 +3237,21 @@
         <v>28</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>137</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>27</v>
@@ -3179,21 +3260,21 @@
         <v>28</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>27</v>
@@ -3202,21 +3283,21 @@
         <v>28</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>27</v>
@@ -3225,21 +3306,21 @@
         <v>28</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>27</v>
@@ -3248,21 +3329,21 @@
         <v>28</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>27</v>
@@ -3271,21 +3352,21 @@
         <v>28</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>27</v>
@@ -3294,21 +3375,21 @@
         <v>28</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>27</v>
@@ -3317,21 +3398,21 @@
         <v>28</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>137</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>27</v>
@@ -3340,21 +3421,21 @@
         <v>28</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>27</v>
@@ -3363,21 +3444,21 @@
         <v>28</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>137</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>27</v>
@@ -3386,21 +3467,21 @@
         <v>28</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>27</v>
@@ -3409,21 +3490,21 @@
         <v>28</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>27</v>
@@ -3432,21 +3513,21 @@
         <v>28</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>27</v>
@@ -3455,21 +3536,21 @@
         <v>28</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>27</v>
@@ -3478,21 +3559,21 @@
         <v>28</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>27</v>
@@ -3501,21 +3582,21 @@
         <v>28</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>137</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>27</v>
@@ -3524,21 +3605,21 @@
         <v>28</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>27</v>
@@ -3547,21 +3628,21 @@
         <v>28</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>137</v>
+        <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>27</v>
@@ -3570,21 +3651,21 @@
         <v>28</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>27</v>
@@ -3593,21 +3674,21 @@
         <v>28</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>137</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>27</v>
@@ -3616,21 +3697,21 @@
         <v>28</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>137</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>27</v>
@@ -3639,21 +3720,21 @@
         <v>28</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>137</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>27</v>
@@ -3662,21 +3743,21 @@
         <v>28</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>27</v>
@@ -3685,21 +3766,21 @@
         <v>28</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>27</v>
@@ -3708,21 +3789,21 @@
         <v>28</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>137</v>
+        <v>292</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>27</v>
@@ -3731,21 +3812,21 @@
         <v>28</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>27</v>
@@ -3754,21 +3835,21 @@
         <v>28</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>27</v>
@@ -3777,21 +3858,21 @@
         <v>28</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>137</v>
+        <v>302</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>27</v>
@@ -3800,21 +3881,21 @@
         <v>28</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>27</v>
@@ -3823,21 +3904,21 @@
         <v>28</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>137</v>
+        <v>292</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>27</v>
@@ -3846,21 +3927,21 @@
         <v>28</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>137</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>27</v>
@@ -3869,21 +3950,21 @@
         <v>28</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>27</v>
@@ -3892,21 +3973,21 @@
         <v>28</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>27</v>
@@ -3915,21 +3996,21 @@
         <v>28</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>27</v>
@@ -3938,44 +4019,44 @@
         <v>28</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>27</v>
@@ -3984,21 +4065,21 @@
         <v>28</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>137</v>
+        <v>302</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>27</v>
@@ -4007,21 +4088,21 @@
         <v>28</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>27</v>
@@ -4030,21 +4111,21 @@
         <v>28</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>27</v>
@@ -4053,21 +4134,21 @@
         <v>28</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>27</v>
@@ -4076,7 +4157,7 @@
         <v>28</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4108,10 +4189,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -4122,10 +4203,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -4151,268 +4232,268 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>329</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>334</v>
+        <v>25</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>234</v>
+        <v>365</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>9</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>237</v>
+        <v>31</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -4423,353 +4504,353 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>240</v>
+        <v>363</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>9</v>
+        <v>364</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>243</v>
+        <v>360</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>246</v>
+        <v>361</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>9</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>346</v>
+        <v>35</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>249</v>
+        <v>373</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>9</v>
+        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>252</v>
+        <v>358</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>9</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>255</v>
+        <v>359</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>9</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>350</v>
+        <v>39</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>351</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>258</v>
+        <v>359</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>9</v>
+        <v>380</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>261</v>
+        <v>360</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>264</v>
+        <v>43</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -4780,523 +4861,523 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>364</v>
+        <v>47</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>230</v>
+        <v>351</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>267</v>
+        <v>385</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>9</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>230</v>
+        <v>351</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>270</v>
+        <v>386</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>230</v>
+        <v>351</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>273</v>
+        <v>387</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>9</v>
+        <v>372</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>365</v>
+        <v>51</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>230</v>
+        <v>351</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>276</v>
+        <v>392</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>9</v>
+        <v>376</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>369</v>
+        <v>54</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>230</v>
+        <v>351</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>279</v>
+        <v>385</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>9</v>
+        <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>371</v>
+        <v>58</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>372</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>378</v>
+        <v>62</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>379</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>380</v>
+        <v>66</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>282</v>
+        <v>396</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>9</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>285</v>
+        <v>398</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>9</v>
+        <v>399</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>288</v>
+        <v>400</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>9</v>
+        <v>401</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>291</v>
+        <v>70</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -5307,47 +5388,47 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>294</v>
+        <v>402</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>9</v>
+        <v>403</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>297</v>
+        <v>74</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -5358,183 +5439,183 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>335</v>
+        <v>410</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>300</v>
+        <v>413</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>335</v>
+        <v>414</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>383</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>390</v>
+        <v>353</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>230</v>
+        <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -5545,217 +5626,217 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>306</v>
+        <v>416</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>309</v>
+        <v>396</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>9</v>
+        <v>414</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>312</v>
+        <v>417</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>315</v>
+        <v>396</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>9</v>
+        <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>337</v>
+        <v>86</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>318</v>
+        <v>396</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>9</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>140</v>
+        <v>419</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>146</v>
+        <v>423</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>9</v>
+        <v>424</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>149</v>
+        <v>425</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>9</v>
+        <v>426</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>152</v>
+        <v>427</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>155</v>
+        <v>396</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>9</v>
+        <v>428</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>28</v>
@@ -5766,30 +5847,30 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>161</v>
+        <v>419</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>28</v>
@@ -5800,81 +5881,81 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>167</v>
+        <v>416</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>170</v>
+        <v>396</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>9</v>
+        <v>428</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>173</v>
+        <v>429</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>176</v>
+        <v>396</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>9</v>
+        <v>430</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>28</v>
@@ -5885,98 +5966,98 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>182</v>
+        <v>431</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>185</v>
+        <v>432</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>9</v>
+        <v>434</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>191</v>
+        <v>435</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>194</v>
+        <v>436</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>9</v>
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>197</v>
+        <v>102</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>28</v>
@@ -5987,605 +6068,605 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>200</v>
+        <v>431</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>203</v>
+        <v>439</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>9</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>206</v>
+        <v>441</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>9</v>
+        <v>442</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>209</v>
+        <v>435</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>212</v>
+        <v>419</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>215</v>
+        <v>443</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>9</v>
+        <v>440</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>218</v>
+        <v>444</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>9</v>
+        <v>445</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>221</v>
+        <v>446</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>9</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>224</v>
+        <v>427</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>227</v>
+        <v>448</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>329</v>
+        <v>24</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>391</v>
+        <v>106</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>339</v>
+        <v>421</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>395</v>
+        <v>449</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>339</v>
+        <v>450</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>328</v>
+        <v>451</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>397</v>
+        <v>452</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>335</v>
+        <v>453</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>328</v>
+        <v>451</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>398</v>
+        <v>110</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>399</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>328</v>
+        <v>451</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>25</v>
+        <v>454</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>328</v>
+        <v>451</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>400</v>
+        <v>114</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>401</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>328</v>
+        <v>451</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>403</v>
+        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>328</v>
+        <v>451</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>404</v>
+        <v>456</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>396</v>
+        <v>118</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>406</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>397</v>
+        <v>457</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>398</v>
+        <v>121</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>407</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>31</v>
+        <v>458</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>400</v>
+        <v>459</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>401</v>
+        <v>460</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>402</v>
+        <v>461</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>403</v>
+        <v>462</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>395</v>
+        <v>463</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>408</v>
+        <v>353</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>396</v>
+        <v>464</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>408</v>
+        <v>465</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>397</v>
+        <v>125</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>409</v>
+        <v>353</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>35</v>
+        <v>459</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>410</v>
+        <v>466</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>411</v>
+        <v>467</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>412</v>
+        <v>463</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>396</v>
@@ -6594,52 +6675,52 @@
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>333</v>
+        <v>469</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>397</v>
+        <v>129</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>413</v>
+        <v>353</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>28</v>
@@ -6650,115 +6731,115 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>401</v>
+        <v>353</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>402</v>
+        <v>137</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>403</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>395</v>
+        <v>141</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>415</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>392</v>
+        <v>144</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>396</v>
+        <v>145</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>415</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>392</v>
+        <v>144</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>397</v>
+        <v>149</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>336</v>
+        <v>144</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>337</v>
+        <v>152</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>28</v>
@@ -6769,81 +6850,81 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>338</v>
+        <v>159</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>339</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>332</v>
+        <v>162</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>339</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>334</v>
+        <v>166</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>340</v>
+        <v>169</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>416</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>47</v>
+        <v>173</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>28</v>
@@ -6854,81 +6935,81 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>417</v>
+        <v>177</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>418</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>332</v>
+        <v>181</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>419</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>334</v>
+        <v>185</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>340</v>
+        <v>189</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>409</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>28</v>
@@ -6939,81 +7020,81 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>330</v>
+        <v>196</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>331</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>332</v>
+        <v>199</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>406</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>334</v>
+        <v>203</v>
       </c>
       <c r="D167" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>340</v>
+        <v>206</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>420</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>54</v>
+        <v>209</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>28</v>
@@ -7024,64 +7105,64 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>330</v>
+        <v>212</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>331</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>332</v>
+        <v>216</v>
       </c>
       <c r="D171" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>333</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>334</v>
+        <v>219</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>28</v>
@@ -7092,98 +7173,98 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>336</v>
+        <v>144</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>337</v>
+        <v>225</v>
       </c>
       <c r="D174" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>330</v>
+        <v>228</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>331</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>332</v>
+        <v>231</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>333</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>422</v>
+        <v>234</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>334</v>
+        <v>238</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>28</v>
@@ -7194,285 +7275,285 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>336</v>
+        <v>144</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>355</v>
+        <v>244</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>423</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>24</v>
+        <v>351</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>65</v>
+        <v>392</v>
       </c>
       <c r="D181" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>9</v>
+        <v>376</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>423</v>
+        <v>378</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>424</v>
+        <v>386</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>425</v>
+        <v>353</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>426</v>
+        <v>248</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>427</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>69</v>
+        <v>383</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>428</v>
+        <v>384</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>429</v>
+        <v>356</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>24</v>
+        <v>351</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>73</v>
+        <v>386</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>423</v>
+        <v>472</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>347</v>
+        <v>251</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>348</v>
+        <v>473</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>349</v>
+        <v>474</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="D192" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>432</v>
+        <v>475</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>433</v>
+        <v>386</v>
       </c>
       <c r="D193" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>434</v>
+        <v>353</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="D194" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>335</v>
+        <v>476</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>355</v>
+        <v>254</v>
       </c>
       <c r="D195" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>436</v>
+        <v>9</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>28</v>
@@ -7483,302 +7564,302 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>347</v>
+        <v>392</v>
       </c>
       <c r="D197" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>437</v>
+        <v>385</v>
       </c>
       <c r="D198" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>24</v>
+        <v>351</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="D199" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>438</v>
+        <v>260</v>
       </c>
       <c r="D200" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>355</v>
+        <v>263</v>
       </c>
       <c r="D201" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>436</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>355</v>
+        <v>266</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>440</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>355</v>
+        <v>270</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>440</v>
+        <v>9</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>357</v>
+        <v>273</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="D207" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="D208" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>441</v>
+        <v>478</v>
       </c>
       <c r="D209" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>364</v>
+        <v>480</v>
       </c>
       <c r="D210" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>335</v>
+        <v>481</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
       <c r="D211" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>443</v>
+        <v>353</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>88</v>
+        <v>396</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>9</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>357</v>
+        <v>276</v>
       </c>
       <c r="D213" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>92</v>
+        <v>280</v>
       </c>
       <c r="D214" s="6" t="s">
         <v>28</v>
@@ -7789,183 +7870,183 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="D215" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>355</v>
+        <v>284</v>
       </c>
       <c r="D216" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>443</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="D217" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>355</v>
+        <v>420</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>96</v>
+        <v>483</v>
       </c>
       <c r="D219" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>9</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>365</v>
+        <v>485</v>
       </c>
       <c r="D220" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>335</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>366</v>
+        <v>427</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="D222" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>369</v>
+        <v>287</v>
       </c>
       <c r="D223" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>449</v>
+        <v>290</v>
       </c>
       <c r="D224" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>450</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>99</v>
+        <v>294</v>
       </c>
       <c r="D225" s="6" t="s">
         <v>28</v>
@@ -7976,319 +8057,319 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>365</v>
+        <v>431</v>
       </c>
       <c r="D226" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>371</v>
+        <v>297</v>
       </c>
       <c r="D227" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>372</v>
+        <v>9</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="D228" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>452</v>
+        <v>353</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>369</v>
+        <v>432</v>
       </c>
       <c r="D229" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>335</v>
+        <v>421</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>357</v>
+        <v>487</v>
       </c>
       <c r="D230" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>335</v>
+        <v>488</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="D231" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="D232" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>455</v>
+        <v>300</v>
       </c>
       <c r="D233" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>456</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>364</v>
+        <v>431</v>
       </c>
       <c r="D234" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>380</v>
+        <v>439</v>
       </c>
       <c r="D235" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>102</v>
+        <v>490</v>
       </c>
       <c r="D236" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>9</v>
+        <v>491</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>365</v>
+        <v>435</v>
       </c>
       <c r="D237" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
       <c r="D238" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="D239" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>369</v>
+        <v>423</v>
       </c>
       <c r="D240" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>335</v>
+        <v>424</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="D241" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="D242" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="D243" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>110</v>
+        <v>304</v>
       </c>
       <c r="D244" s="6" t="s">
         <v>28</v>
@@ -8299,47 +8380,47 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="D245" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>463</v>
+        <v>310</v>
       </c>
       <c r="D246" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>464</v>
+        <v>9</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>113</v>
+        <v>313</v>
       </c>
       <c r="D247" s="6" t="s">
         <v>28</v>
@@ -8350,251 +8431,251 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>465</v>
+        <v>316</v>
       </c>
       <c r="D248" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>117</v>
+        <v>458</v>
       </c>
       <c r="D249" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>381</v>
+        <v>319</v>
       </c>
       <c r="D250" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>382</v>
+        <v>458</v>
       </c>
       <c r="D251" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>384</v>
+        <v>459</v>
       </c>
       <c r="D252" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>385</v>
+        <v>460</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>386</v>
+        <v>461</v>
       </c>
       <c r="D253" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>335</v>
+        <v>462</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>387</v>
+        <v>463</v>
       </c>
       <c r="D254" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>466</v>
+        <v>353</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>121</v>
+        <v>464</v>
       </c>
       <c r="D255" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>9</v>
+        <v>494</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>381</v>
+        <v>322</v>
       </c>
       <c r="D256" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>382</v>
+        <v>458</v>
       </c>
       <c r="D257" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>389</v>
+        <v>459</v>
       </c>
       <c r="D258" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>390</v>
+        <v>460</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>386</v>
+        <v>466</v>
       </c>
       <c r="D259" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>335</v>
+        <v>467</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="D260" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="D261" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>467</v>
+        <v>9</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>125</v>
+        <v>328</v>
       </c>
       <c r="D262" s="6" t="s">
         <v>28</v>
@@ -8605,30 +8686,30 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="D263" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>128</v>
+        <v>334</v>
       </c>
       <c r="D264" s="6" t="s">
         <v>28</v>
@@ -8639,10 +8720,10 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>337</v>
@@ -8651,35 +8732,35 @@
         <v>28</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>24</v>
+        <v>382</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>132</v>
+        <v>383</v>
       </c>
       <c r="D266" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
-        <v>3</v>
+        <v>471</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>135</v>
+        <v>340</v>
       </c>
       <c r="D267" s="6" t="s">
         <v>28</v>

--- a/reports/Master_Report.xlsx
+++ b/reports/Master_Report.xlsx
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 5:20:48 AM</t>
+    <t>6/16/2026, 5:29:22 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>28.65s</t>
+    <t>28.76s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -784,6 +784,9 @@
     <t>Error label displays when email format is invalid</t>
   </si>
   <si>
+    <t>0.20s</t>
+  </si>
+  <si>
     <t>TC-APP-04</t>
   </si>
   <si>
@@ -802,6 +805,9 @@
     <t>Dashboard balance, income, and expense summary widgets render</t>
   </si>
   <si>
+    <t>0.32s</t>
+  </si>
+  <si>
     <t>TC-APP-06</t>
   </si>
   <si>
@@ -811,6 +817,9 @@
     <t>Balance summary card resolves within view limits</t>
   </si>
   <si>
+    <t>0.24s</t>
+  </si>
+  <si>
     <t>TC-APP-07</t>
   </si>
   <si>
@@ -820,9 +829,6 @@
     <t>Pull to refresh updates transaction listings from background storage</t>
   </si>
   <si>
-    <t>0.20s</t>
-  </si>
-  <si>
     <t>TC-APP-08</t>
   </si>
   <si>
@@ -850,7 +856,7 @@
     <t>Income fields accept numeric and descriptive inputs</t>
   </si>
   <si>
-    <t>0.32s</t>
+    <t>0.17s</t>
   </si>
   <si>
     <t>TC-APP-11</t>
@@ -862,87 +868,81 @@
     <t>Missing amount triggers mobile error highlights</t>
   </si>
   <si>
+    <t>TC-APP-12</t>
+  </si>
+  <si>
+    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
+  </si>
+  <si>
+    <t>Expense sheet slides up with focus on Category dropdown</t>
+  </si>
+  <si>
+    <t>TC-APP-13</t>
+  </si>
+  <si>
+    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
+  </si>
+  <si>
+    <t>Expense logging works and decreases overall dashboard balance</t>
+  </si>
+  <si>
+    <t>TC-APP-14</t>
+  </si>
+  <si>
+    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
+  </si>
+  <si>
+    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
+  </si>
+  <si>
+    <t>TC-APP-15</t>
+  </si>
+  <si>
+    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
+  </si>
+  <si>
+    <t>Soft keyboard changes to numeric layout on amount field focus</t>
+  </si>
+  <si>
+    <t>TC-APP-16</t>
+  </si>
+  <si>
+    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
+  </si>
+  <si>
+    <t>Active budget progress limiters are visible</t>
+  </si>
+  <si>
+    <t>TC-APP-17</t>
+  </si>
+  <si>
+    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
+  </si>
+  <si>
+    <t>Progress bar limits adjust to new budget configurations</t>
+  </si>
+  <si>
+    <t>TC-APP-18</t>
+  </si>
+  <si>
+    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
+  </si>
+  <si>
+    <t>Alert popup loads when transaction breaches designated cap threshold</t>
+  </si>
+  <si>
+    <t>TC-APP-19</t>
+  </si>
+  <si>
+    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
+  </si>
+  <si>
+    <t>Distribution chart switches between absolute values and percentages</t>
+  </si>
+  <si>
     <t>0.21s</t>
   </si>
   <si>
-    <t>TC-APP-12</t>
-  </si>
-  <si>
-    <t>TC-APP-12: Verify opening Add Expense sheets view modal interface</t>
-  </si>
-  <si>
-    <t>Expense sheet slides up with focus on Category dropdown</t>
-  </si>
-  <si>
-    <t>TC-APP-13</t>
-  </si>
-  <si>
-    <t>TC-APP-13: Verify add expense transaction amount and description entry</t>
-  </si>
-  <si>
-    <t>Expense logging works and decreases overall dashboard balance</t>
-  </si>
-  <si>
-    <t>TC-APP-14</t>
-  </si>
-  <si>
-    <t>TC-APP-14: Verify expense category dropdown lists standard budget segments</t>
-  </si>
-  <si>
-    <t>Dropdown contains Food, Utilities, Entertainment, Rent, Shopping</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-APP-15</t>
-  </si>
-  <si>
-    <t>TC-APP-15: Verify numeric decimal keyboard display focus on amount input field</t>
-  </si>
-  <si>
-    <t>Soft keyboard changes to numeric layout on amount field focus</t>
-  </si>
-  <si>
-    <t>TC-APP-16</t>
-  </si>
-  <si>
-    <t>TC-APP-16: Verify category budgets progress visualizer bars render</t>
-  </si>
-  <si>
-    <t>Active budget progress limiters are visible</t>
-  </si>
-  <si>
-    <t>TC-APP-17</t>
-  </si>
-  <si>
-    <t>TC-APP-17: Verify configuring category budget cap limits triggers UI update</t>
-  </si>
-  <si>
-    <t>Progress bar limits adjust to new budget configurations</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-APP-18</t>
-  </si>
-  <si>
-    <t>TC-APP-18: Verify budget cap exceeded mobile warning modal triggers</t>
-  </si>
-  <si>
-    <t>Alert popup loads when transaction breaches designated cap threshold</t>
-  </si>
-  <si>
-    <t>TC-APP-19</t>
-  </si>
-  <si>
-    <t>TC-APP-19: Verify category analytics distribution share toggle charts</t>
-  </si>
-  <si>
-    <t>Distribution chart switches between absolute values and percentages</t>
-  </si>
-  <si>
     <t>TC-APP-20</t>
   </si>
   <si>
@@ -1004,6 +1004,9 @@
   </si>
   <si>
     <t>Dialog queries permissions access to camera device for receipts scan</t>
+  </si>
+  <si>
+    <t>0.27s</t>
   </si>
   <si>
     <t>TC-APP-27</t>
@@ -1450,9 +1453,6 @@
   </si>
   <si>
     <t>6/16/2026, 5:20:46 AM</t>
-  </si>
-  <si>
-    <t>6/16/2026, 5:20:47 AM</t>
   </si>
   <si>
     <t>Text found (Simulated): "Validation error: Fields required"</t>
@@ -3490,7 +3490,7 @@
         <v>28</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>179</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3513,7 +3513,7 @@
         <v>28</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3536,21 +3536,21 @@
         <v>28</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>56</v>
+        <v>256</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>27</v>
@@ -3559,21 +3559,21 @@
         <v>28</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>27</v>
@@ -3582,21 +3582,21 @@
         <v>28</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>27</v>
@@ -3605,21 +3605,21 @@
         <v>28</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>164</v>
+        <v>267</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>27</v>
@@ -3628,21 +3628,21 @@
         <v>28</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>268</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>27</v>
@@ -3651,21 +3651,21 @@
         <v>28</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>27</v>
@@ -3674,21 +3674,21 @@
         <v>28</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>214</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>27</v>
@@ -3697,21 +3697,21 @@
         <v>28</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>27</v>
@@ -3720,21 +3720,21 @@
         <v>28</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>282</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>27</v>
@@ -3743,21 +3743,21 @@
         <v>28</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>27</v>
@@ -3766,21 +3766,21 @@
         <v>28</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>27</v>
@@ -3789,7 +3789,7 @@
         <v>28</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>292</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3812,7 +3812,7 @@
         <v>28</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3835,7 +3835,7 @@
         <v>28</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3858,22 +3858,22 @@
         <v>28</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>302</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="E79" s="3" t="s">
         <v>27</v>
       </c>
@@ -3881,30 +3881,30 @@
         <v>28</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="E80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" s="5" t="s">
         <v>308</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3927,7 +3927,7 @@
         <v>28</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>236</v>
+        <v>131</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -3950,7 +3950,7 @@
         <v>28</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -3973,7 +3973,7 @@
         <v>28</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>131</v>
+        <v>280</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3996,7 +3996,7 @@
         <v>28</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
         <v>28</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4042,7 +4042,7 @@
         <v>28</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>302</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4065,21 +4065,21 @@
         <v>28</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>27</v>
@@ -4088,21 +4088,21 @@
         <v>28</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>27</v>
@@ -4111,21 +4111,21 @@
         <v>28</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>49</v>
+        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>27</v>
@@ -4134,21 +4134,21 @@
         <v>28</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>27</v>
@@ -4157,7 +4157,7 @@
         <v>28</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -4189,10 +4189,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -4203,10 +4203,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -4232,143 +4232,143 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
@@ -4385,109 +4385,109 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
@@ -4504,109 +4504,109 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
@@ -4623,109 +4623,109 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
@@ -4742,109 +4742,109 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
@@ -4861,75 +4861,75 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
@@ -4946,75 +4946,75 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
@@ -5031,75 +5031,75 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
@@ -5116,58 +5116,58 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
@@ -5184,92 +5184,92 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
@@ -5286,24 +5286,24 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
@@ -5320,58 +5320,58 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
@@ -5388,41 +5388,41 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
@@ -5439,126 +5439,126 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>24</v>
@@ -5575,41 +5575,41 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>405</v>
-      </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
@@ -5626,75 +5626,75 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>24</v>
@@ -5711,126 +5711,126 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>24</v>
@@ -5847,24 +5847,24 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>24</v>
@@ -5881,75 +5881,75 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>24</v>
@@ -5966,92 +5966,92 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>24</v>
@@ -6068,177 +6068,177 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>24</v>
@@ -6255,92 +6255,92 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>24</v>
@@ -6357,24 +6357,24 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>24</v>
@@ -6391,41 +6391,41 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>24</v>
@@ -6442,24 +6442,24 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>24</v>
@@ -6476,92 +6476,92 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
@@ -6578,109 +6578,109 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>24</v>
@@ -6697,24 +6697,24 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>24</v>
@@ -6731,24 +6731,24 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>24</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>24</v>
@@ -6782,7 +6782,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>144</v>
@@ -6799,7 +6799,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>144</v>
@@ -6816,7 +6816,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>144</v>
@@ -6833,7 +6833,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>144</v>
@@ -6850,7 +6850,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>144</v>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>144</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>144</v>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>144</v>
@@ -6918,7 +6918,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>144</v>
@@ -6935,7 +6935,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>144</v>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>144</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>144</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>144</v>
@@ -7003,7 +7003,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>144</v>
@@ -7020,7 +7020,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>144</v>
@@ -7037,7 +7037,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>144</v>
@@ -7054,7 +7054,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>144</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>144</v>
@@ -7088,7 +7088,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>144</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>144</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>144</v>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>144</v>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>144</v>
@@ -7173,7 +7173,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>144</v>
@@ -7190,7 +7190,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>144</v>
@@ -7207,7 +7207,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>144</v>
@@ -7224,7 +7224,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>144</v>
@@ -7241,7 +7241,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>144</v>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>144</v>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>144</v>
@@ -7292,58 +7292,58 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D181" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>247</v>
@@ -7360,81 +7360,81 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>28</v>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>247</v>
@@ -7462,10 +7462,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>473</v>
@@ -7479,13 +7479,13 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D192" s="6" t="s">
         <v>28</v>
@@ -7496,30 +7496,30 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D193" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D194" s="6" t="s">
         <v>28</v>
@@ -7530,7 +7530,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>247</v>
@@ -7547,13 +7547,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>28</v>
@@ -7564,64 +7564,64 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D197" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D198" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D199" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D200" s="6" t="s">
         <v>28</v>
@@ -7632,13 +7632,13 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D201" s="6" t="s">
         <v>28</v>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>477</v>
@@ -7661,18 +7661,18 @@
         <v>28</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>28</v>
@@ -7683,30 +7683,30 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>28</v>
@@ -7717,13 +7717,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>28</v>
@@ -7734,44 +7734,44 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D207" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D208" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>478</v>
@@ -7785,10 +7785,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>480</v>
@@ -7802,30 +7802,30 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D211" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>28</v>
@@ -7836,13 +7836,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D213" s="6" t="s">
         <v>28</v>
@@ -7853,13 +7853,13 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D214" s="6" t="s">
         <v>28</v>
@@ -7870,30 +7870,30 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D215" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D216" s="6" t="s">
         <v>28</v>
@@ -7904,44 +7904,44 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D217" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>483</v>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>485</v>
@@ -7972,30 +7972,30 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D222" s="6" t="s">
         <v>28</v>
@@ -8006,13 +8006,13 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D223" s="6" t="s">
         <v>28</v>
@@ -8023,13 +8023,13 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D224" s="6" t="s">
         <v>28</v>
@@ -8040,7 +8040,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>247</v>
@@ -8057,24 +8057,24 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D226" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>247</v>
@@ -8091,44 +8091,44 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D228" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D229" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>487</v>
@@ -8142,27 +8142,27 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D231" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>489</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>247</v>
@@ -8193,44 +8193,44 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D234" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D235" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>490</v>
@@ -8244,78 +8244,78 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D237" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D238" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D239" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D240" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>492</v>
@@ -8329,47 +8329,47 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D242" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D243" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D244" s="6" t="s">
         <v>28</v>
@@ -8380,13 +8380,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D245" s="6" t="s">
         <v>28</v>
@@ -8397,7 +8397,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>247</v>
@@ -8414,7 +8414,7 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>247</v>
@@ -8431,7 +8431,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>247</v>
@@ -8448,24 +8448,24 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D249" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>247</v>
@@ -8482,81 +8482,81 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D251" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D252" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D253" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D254" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D255" s="6" t="s">
         <v>28</v>
@@ -8567,7 +8567,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>247</v>
@@ -8584,75 +8584,75 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D257" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D258" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D259" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D260" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>247</v>
@@ -8669,7 +8669,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>247</v>
@@ -8686,13 +8686,13 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D263" s="6" t="s">
         <v>28</v>
@@ -8703,13 +8703,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D264" s="6" t="s">
         <v>28</v>
@@ -8720,13 +8720,13 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D265" s="6" t="s">
         <v>28</v>
@@ -8737,30 +8737,30 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D266" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
-        <v>471</v>
+        <v>3</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D267" s="6" t="s">
         <v>28</v>
